--- a/report/Figure/Cycle-by-Cycle.xlsx
+++ b/report/Figure/Cycle-by-Cycle.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\DSP-IN-VLSI-Final\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\DSP-IN-VLSI-Final\report\Figure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B81F05-B47B-4EB9-9541-9E2178B84A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933636D3-94FC-4173-A3F4-84DE1382F59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="123">
   <si>
     <t>Cycle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -520,6 +520,14 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Output Buffer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> U Register</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -562,7 +570,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,12 +628,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF5353"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -802,7 +804,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -813,10 +815,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFCD"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FFE6E7F4"/>
       <color rgb="FFFF5353"/>
-      <color rgb="FFFFFFCD"/>
       <color rgb="FFCCECFF"/>
       <color rgb="FFCCCCFF"/>
     </mruColors>
@@ -830,6 +832,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>363739</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>18495</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>452638</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>27620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="圖片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8562C367-58F5-4922-2B12-A17C91C0BBA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8285826" y="394563"/>
+          <a:ext cx="7382152" cy="3954756"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3994,14 +4062,14 @@
       <c r="G3" s="20"/>
       <c r="H3" s="20"/>
       <c r="I3" s="21" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
       <c r="N3" s="22" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
@@ -5039,5 +5107,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/report/Figure/Cycle-by-Cycle.xlsx
+++ b/report/Figure/Cycle-by-Cycle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\DSP-IN-VLSI-Final\report\Figure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933636D3-94FC-4173-A3F4-84DE1382F59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9CF9BE-A1AA-4C95-A385-FB7836998FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="123">
   <si>
     <t>Cycle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -747,6 +747,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -804,9 +807,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -838,23 +838,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>363739</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>18495</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>452638</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>27620</xdr:rowOff>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="圖片 2">
+        <xdr:cNvPr id="2" name="圖片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8562C367-58F5-4922-2B12-A17C91C0BBA3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8433AAA2-BB1E-CEC7-DF9A-B427C2386BBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -877,8 +877,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8285826" y="394563"/>
-          <a:ext cx="7382152" cy="3954756"/>
+          <a:off x="8464550" y="374650"/>
+          <a:ext cx="7353300" cy="3943350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1188,45 +1188,45 @@
     <row r="1" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:29" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="25" t="s">
+      <c r="D2" s="33"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="34" t="s">
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="28" t="s">
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="25" t="s">
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="25" t="s">
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="28"/>
     </row>
     <row r="3" spans="2:29" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
@@ -2328,60 +2328,60 @@
     <row r="1" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="25" t="s">
+      <c r="D2" s="33"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="34" t="s">
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="28" t="s">
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="25" t="s">
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="25" t="s">
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
-      <c r="AH2" s="26"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="26"/>
-      <c r="AK2" s="26"/>
-      <c r="AL2" s="26"/>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="31" t="s">
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="33"/>
+      <c r="AO2" s="33"/>
+      <c r="AP2" s="34"/>
     </row>
     <row r="3" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
@@ -4051,34 +4051,34 @@
       <c r="B3" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="21" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="22" t="s">
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="25"/>
     </row>
     <row r="4" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="12" t="s">
@@ -4146,7 +4146,7 @@
       </c>
     </row>
     <row r="5" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="37">
+      <c r="B5" s="18">
         <v>0</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -4195,7 +4195,7 @@
       </c>
     </row>
     <row r="6" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="37">
+      <c r="B6" s="18">
         <v>1</v>
       </c>
       <c r="C6" s="14" t="s">
@@ -4244,7 +4244,7 @@
       </c>
     </row>
     <row r="7" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="37">
+      <c r="B7" s="18">
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
@@ -5055,7 +5055,7 @@
       <c r="G22" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="16" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="15" t="s">
@@ -5067,7 +5067,9 @@
       <c r="K22" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="15"/>
+      <c r="L22" s="16" t="s">
+        <v>16</v>
+      </c>
       <c r="M22" s="15"/>
       <c r="N22" s="13" t="s">
         <v>9</v>
